--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.49685920992368</v>
+        <v>2.518239621612597</v>
       </c>
       <c r="D2" t="n">
-        <v>8.178632937780371</v>
+        <v>1.32902785238931</v>
       </c>
       <c r="E2" t="n">
-        <v>9.534663270963989</v>
+        <v>1.549382781531648</v>
       </c>
       <c r="F2" t="n">
-        <v>7.857349144189332</v>
+        <v>1.276819235930766</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.27292538729318</v>
+        <v>5.569350375435142</v>
       </c>
       <c r="D3" t="n">
-        <v>24.26518344542312</v>
+        <v>3.943092309881257</v>
       </c>
       <c r="E3" t="n">
-        <v>9.534663270963989</v>
+        <v>1.549382781531648</v>
       </c>
       <c r="F3" t="n">
-        <v>7.857349144189332</v>
+        <v>1.276819235930766</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.9135506105439</v>
+        <v>5.998451974213384</v>
       </c>
       <c r="D4" t="n">
-        <v>7.071067811865476</v>
+        <v>1.14904851942814</v>
       </c>
       <c r="E4" t="n">
-        <v>9.534663270963989</v>
+        <v>1.549382781531648</v>
       </c>
       <c r="F4" t="n">
-        <v>7.857349144189332</v>
+        <v>1.276819235930766</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
